--- a/output/deployment_metadata.xlsx
+++ b/output/deployment_metadata.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-11 20:39</t>
+          <t>2026-08-12 20:35</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
